--- a/output/pdf_financials_xlsx/TIH.xlsx
+++ b/output/pdf_financials_xlsx/TIH.xlsx
@@ -2539,16 +2539,16 @@
         <v>0.206957</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.174089</v>
+        <v>0.075319</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.383</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>70.76900000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>85.962</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
@@ -2556,16 +2556,16 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>188.735</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>160.507</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>345.434</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>365.589</v>
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         <v>0.206957</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.174089</v>
+        <v>0.075319</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.383</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>70.76900000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>85.962</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
@@ -2688,16 +2688,16 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>188.735</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>160.507</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>345.434</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>365.589</v>
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -67268,7 +67268,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -68494,7 +68494,7 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -70294,7 +70294,7 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
@@ -77779,7 +77779,7 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E690" s="5" t="n">

--- a/output/pdf_financials_xlsx/TIH.xlsx
+++ b/output/pdf_financials_xlsx/TIH.xlsx
@@ -7617,16 +7617,16 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>1.521</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>3.185</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>9.506</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.737</v>
       </c>
       <c r="N112" s="1" t="inlineStr">
         <is>
@@ -7639,13 +7639,13 @@
         </is>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.010297</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.003431</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.016662</v>
       </c>
     </row>
     <row r="113">
@@ -42970,7 +42970,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
